--- a/Yellow Kaizo Patch and Important Documents/Items (TMs and Key).xlsx
+++ b/Yellow Kaizo Patch and Important Documents/Items (TMs and Key).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Yellow-Kaizo\Yellow Kaizo Patch and Important Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5843D4DE-600D-4C5E-89C2-72938E72492D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF141BC7-7015-4222-8124-3C26657D170B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="285" windowWidth="11520" windowHeight="10635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TMHMs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="204">
   <si>
     <t>#</t>
   </si>
@@ -112,9 +112,6 @@
   </si>
   <si>
     <t>Swords Dance</t>
-  </si>
-  <si>
-    <t>Silph Co. (7F, E room)</t>
   </si>
   <si>
     <t>Whirlwind</t>
@@ -1346,11 +1343,11 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="32" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>30</v>
+        <v>199</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>10</v>
@@ -1370,10 +1367,10 @@
         <v>17</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>10</v>
@@ -1393,10 +1390,10 @@
         <v>20</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>26</v>
@@ -1413,16 +1410,16 @@
         <v>23</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="D12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="F12" s="16">
         <v>4000</v>
@@ -1436,13 +1433,13 @@
         <v>23</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>26</v>
@@ -1459,13 +1456,13 @@
         <v>23</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>43</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>44</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>10</v>
@@ -1482,13 +1479,13 @@
         <v>23</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>26</v>
@@ -1505,16 +1502,16 @@
         <v>23</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="D16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="E16" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F16" s="16">
         <v>4000</v>
@@ -1528,16 +1525,16 @@
         <v>23</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="D17" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="F17" s="16">
         <v>2000</v>
@@ -1551,13 +1548,13 @@
         <v>23</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>10</v>
@@ -1574,13 +1571,13 @@
         <v>23</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>60</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>10</v>
@@ -1597,13 +1594,13 @@
         <v>23</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>10</v>
@@ -1620,22 +1617,22 @@
         <v>23</v>
       </c>
       <c r="B21" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="D21" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="F21" s="16">
         <v>111100</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="12.75">
@@ -1643,13 +1640,13 @@
         <v>23</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>70</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>10</v>
@@ -1666,13 +1663,13 @@
         <v>23</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>26</v>
@@ -1689,13 +1686,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>10</v>
@@ -1712,16 +1709,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="D25" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="E25" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F25" s="17">
         <v>3000</v>
@@ -1735,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>82</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>10</v>
@@ -1758,13 +1755,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="D27" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>26</v>
@@ -1781,13 +1778,13 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>10</v>
@@ -1804,13 +1801,13 @@
         <v>23</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="D29" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>10</v>
@@ -1827,13 +1824,13 @@
         <v>23</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>10</v>
@@ -1850,13 +1847,13 @@
         <v>23</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="D31" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>10</v>
@@ -1873,13 +1870,13 @@
         <v>23</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="D32" s="9" t="s">
         <v>96</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>97</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>10</v>
@@ -1896,13 +1893,13 @@
         <v>23</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="D33" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>10</v>
@@ -1919,13 +1916,13 @@
         <v>23</v>
       </c>
       <c r="B34" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="D34" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>26</v>
@@ -1942,13 +1939,13 @@
         <v>23</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="D35" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>10</v>
@@ -1965,16 +1962,16 @@
         <v>23</v>
       </c>
       <c r="B36" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="D36" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>109</v>
-      </c>
       <c r="E36" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F36" s="16">
         <v>1000</v>
@@ -1988,13 +1985,13 @@
         <v>23</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="D37" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>10</v>
@@ -2011,13 +2008,13 @@
         <v>23</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="D38" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>10</v>
@@ -2034,13 +2031,13 @@
         <v>23</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="D39" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>118</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>26</v>
@@ -2057,13 +2054,13 @@
         <v>23</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="D40" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>10</v>
@@ -2080,13 +2077,13 @@
         <v>23</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="D41" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>10</v>
@@ -2103,13 +2100,13 @@
         <v>23</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="D42" s="9" t="s">
         <v>126</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>127</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>10</v>
@@ -2126,13 +2123,13 @@
         <v>23</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="D43" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>26</v>
@@ -2149,16 +2146,16 @@
         <v>23</v>
       </c>
       <c r="B44" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="D44" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="E44" s="15" t="s">
         <v>133</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>134</v>
       </c>
       <c r="F44" s="16">
         <v>5000</v>
@@ -2172,16 +2169,16 @@
         <v>23</v>
       </c>
       <c r="B45" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="D45" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>137</v>
-      </c>
       <c r="E45" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F45" s="16">
         <v>2000</v>
@@ -2195,13 +2192,13 @@
         <v>23</v>
       </c>
       <c r="B46" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="D46" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>10</v>
@@ -2218,13 +2215,13 @@
         <v>23</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="D47" s="9" t="s">
         <v>142</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>143</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>10</v>
@@ -2241,13 +2238,13 @@
         <v>23</v>
       </c>
       <c r="B48" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="D48" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>10</v>
@@ -2264,13 +2261,13 @@
         <v>23</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="D49" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>10</v>
@@ -2287,13 +2284,13 @@
         <v>23</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="D50" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>10</v>
@@ -2310,13 +2307,13 @@
         <v>23</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="D51" s="9" t="s">
         <v>154</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>155</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>10</v>
@@ -2333,16 +2330,16 @@
         <v>23</v>
       </c>
       <c r="B52" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="D52" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>158</v>
-      </c>
       <c r="E52" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F52" s="16">
         <v>4000</v>
@@ -2356,13 +2353,13 @@
         <v>23</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="D53" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>10</v>
@@ -2379,22 +2376,22 @@
         <v>23</v>
       </c>
       <c r="B54" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="D54" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>164</v>
-      </c>
       <c r="E54" s="20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F54" s="21">
         <v>66000</v>
       </c>
       <c r="G54" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="12.75">
@@ -2402,16 +2399,16 @@
         <v>23</v>
       </c>
       <c r="B55" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C55" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="D55" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>168</v>
-      </c>
       <c r="E55" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F55" s="21">
         <v>4000</v>
@@ -2425,22 +2422,22 @@
         <v>23</v>
       </c>
       <c r="B56" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="D56" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="G56" s="8" t="s">
         <v>170</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1">
@@ -2448,13 +2445,13 @@
         <v>23</v>
       </c>
       <c r="B57" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C57" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="C57" s="32" t="s">
-        <v>196</v>
-      </c>
       <c r="D57" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>10</v>
@@ -2492,10 +2489,10 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
@@ -2509,13 +2506,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>176</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>10</v>
@@ -2526,16 +2523,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="9" t="s">
         <v>179</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="E3" s="10">
         <v>2100</v>
@@ -2543,16 +2540,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>182</v>
-      </c>
       <c r="D4" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E4" s="10">
         <v>2100</v>
@@ -2560,16 +2557,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E5" s="10">
         <v>2100</v>
@@ -2577,16 +2574,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E6" s="10">
         <v>2100</v>
@@ -2594,16 +2591,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E7" s="10">
         <v>2100</v>
@@ -2611,13 +2608,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>187</v>
-      </c>
       <c r="C8" s="31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>10</v>
@@ -2628,13 +2625,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>10</v>
@@ -2645,13 +2642,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>189</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>190</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>10</v>
@@ -2662,13 +2659,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B11" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="31" t="s">
         <v>201</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>202</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>10</v>
@@ -2708,11 +2705,11 @@
     <row r="2" spans="1:5">
       <c r="A2" s="26"/>
       <c r="B2" s="27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E2" s="29"/>
     </row>
@@ -2721,7 +2718,7 @@
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
       <c r="D3" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E3" s="25"/>
     </row>
@@ -2730,7 +2727,7 @@
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
       <c r="D4" s="30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E4" s="25"/>
     </row>
